--- a/backend/data/financials_by_company/088350.KS.xlsx
+++ b/backend/data/financials_by_company/088350.KS.xlsx
@@ -627,484 +627,484 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-5067301485.846427</v>
+        <v>8077658433.431293</v>
       </c>
       <c r="C2" t="n">
-        <v>0.261714</v>
+        <v>0.246812</v>
       </c>
       <c r="D2" t="n">
-        <v>-19362000000</v>
+        <v>32728000000</v>
       </c>
       <c r="E2" t="n">
-        <v>-19362000000</v>
+        <v>32728000000</v>
       </c>
       <c r="F2" t="n">
-        <v>737253509030</v>
+        <v>1191311383170</v>
       </c>
       <c r="G2" t="n">
-        <v>195800000000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1667469897590</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-494481814000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>494481814000</v>
-      </c>
+        <v>275814000000</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>3974476131910</v>
+        <v>3628042437350</v>
       </c>
       <c r="L2" t="n">
-        <v>751548207544.1536</v>
+        <v>1166661041603.431</v>
       </c>
       <c r="M2" t="n">
-        <v>737253509030</v>
+        <v>1191311383170</v>
       </c>
       <c r="N2" t="n">
-        <v>15483541484310</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>19471829729240</v>
+      </c>
+      <c r="O2" t="n">
+        <v>12515000000</v>
+      </c>
       <c r="P2" t="n">
-        <v>787664005</v>
+        <v>818770710</v>
       </c>
       <c r="Q2" t="n">
-        <v>757695274</v>
+        <v>818770710</v>
       </c>
       <c r="R2" t="n">
-        <v>936</v>
+        <v>1455</v>
       </c>
       <c r="S2" t="n">
-        <v>936</v>
+        <v>1455</v>
       </c>
       <c r="T2" t="n">
-        <v>737253509030</v>
+        <v>1191311383170</v>
       </c>
       <c r="U2" t="n">
-        <v>737253509030</v>
+        <v>1191311383170</v>
       </c>
       <c r="V2" t="n">
-        <v>-128747473070</v>
+        <v>-57848851760</v>
       </c>
       <c r="W2" t="n">
-        <v>866000982110</v>
+        <v>1249160234930</v>
       </c>
       <c r="X2" t="n">
-        <v>866000982110</v>
+        <v>1249160234930</v>
       </c>
       <c r="Y2" t="n">
-        <v>306987101480</v>
+        <v>409336709560</v>
       </c>
       <c r="Z2" t="n">
-        <v>1172988083590</v>
+        <v>1658496944490</v>
       </c>
       <c r="AA2" t="n">
-        <v>2830955223050</v>
+        <v>2039880662320</v>
       </c>
       <c r="AB2" t="n">
-        <v>-19362000000</v>
+        <v>32728000000</v>
       </c>
       <c r="AC2" t="n">
-        <v>13182000000</v>
+        <v>-34475000000</v>
       </c>
       <c r="AD2" t="n">
-        <v>6180000000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-494481814000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>494481814000</v>
-      </c>
+        <v>1747000000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>1353915582660</v>
+        <v>346425566570</v>
       </c>
       <c r="AH2" t="n">
-        <v>83507000000</v>
+        <v>102749000000</v>
       </c>
       <c r="AI2" t="n">
-        <v>83507000000</v>
+        <v>102749000000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>389948006230</v>
+        <v>642608333890</v>
       </c>
       <c r="AK2" t="n">
-        <v>389948006230</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>642608333890</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>12515000000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>16656529568710</v>
+        <v>21130326673530</v>
       </c>
       <c r="AN2" t="n">
-        <v>16656529568710</v>
+        <v>21130326673530</v>
       </c>
       <c r="AO2" t="n">
-        <v>13211637081420</v>
+        <v>11594854561460</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>10967950997.25201</v>
+        <v>12904701642.74245</v>
       </c>
       <c r="C3" t="n">
-        <v>0.234945</v>
+        <v>0.15154</v>
       </c>
       <c r="D3" t="n">
-        <v>46683000000</v>
+        <v>85157000000</v>
       </c>
       <c r="E3" t="n">
-        <v>46683000000</v>
+        <v>85157000000</v>
       </c>
       <c r="F3" t="n">
-        <v>758479879640</v>
+        <v>1030328630870</v>
       </c>
       <c r="G3" t="n">
-        <v>162205000000</v>
+        <v>253500000000</v>
       </c>
       <c r="H3" t="n">
-        <v>1553048024760</v>
+        <v>1650837751600</v>
       </c>
       <c r="I3" t="n">
-        <v>-473411800000</v>
+        <v>-271305677000</v>
       </c>
       <c r="J3" t="n">
-        <v>473411800000</v>
+        <v>271305677000</v>
       </c>
       <c r="K3" t="n">
-        <v>3983930092550</v>
+        <v>4219288859890</v>
       </c>
       <c r="L3" t="n">
-        <v>722764830637.252</v>
+        <v>958076332512.7424</v>
       </c>
       <c r="M3" t="n">
-        <v>758479879640</v>
+        <v>1030328630870</v>
       </c>
       <c r="N3" t="n">
-        <v>16095126952560</v>
-      </c>
-      <c r="O3" t="inlineStr"/>
+        <v>12699670426020</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5119000000</v>
+      </c>
       <c r="P3" t="n">
-        <v>795052285</v>
+        <v>824922843</v>
       </c>
       <c r="Q3" t="n">
-        <v>795052285</v>
+        <v>824922843</v>
       </c>
       <c r="R3" t="n">
-        <v>954</v>
+        <v>1249</v>
       </c>
       <c r="S3" t="n">
-        <v>954</v>
+        <v>1249</v>
       </c>
       <c r="T3" t="n">
-        <v>758479879640</v>
+        <v>1030328630870</v>
       </c>
       <c r="U3" t="n">
-        <v>758479879640</v>
+        <v>1030328630870</v>
       </c>
       <c r="V3" t="n">
-        <v>-67500898620</v>
+        <v>-140148993360</v>
       </c>
       <c r="W3" t="n">
-        <v>825980778270</v>
+        <v>1170477624230</v>
       </c>
       <c r="X3" t="n">
-        <v>825980778270</v>
+        <v>1170477624230</v>
       </c>
       <c r="Y3" t="n">
-        <v>253655446480</v>
+        <v>209054450360</v>
       </c>
       <c r="Z3" t="n">
-        <v>1079636224760</v>
+        <v>1379532074600</v>
       </c>
       <c r="AA3" t="n">
-        <v>1081664813150</v>
+        <v>948652191560</v>
       </c>
       <c r="AB3" t="n">
-        <v>46683000000</v>
+        <v>85157000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-53722000000</v>
+        <v>-87405000000</v>
       </c>
       <c r="AD3" t="n">
-        <v>7039000000</v>
+        <v>2248000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-473411800000</v>
+        <v>-271305677000</v>
       </c>
       <c r="AF3" t="n">
-        <v>473411800000</v>
+        <v>271305677000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1182527486350</v>
+        <v>786612170480</v>
       </c>
       <c r="AH3" t="n">
-        <v>77826000000</v>
+        <v>52992000000</v>
       </c>
       <c r="AI3" t="n">
-        <v>77826000000</v>
+        <v>52992000000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>349706323650</v>
+        <v>331243973680</v>
       </c>
       <c r="AK3" t="n">
-        <v>349706323650</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>331243973680</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>5119000000</v>
+      </c>
       <c r="AM3" t="n">
-        <v>17174763176510</v>
+        <v>14079202500510</v>
       </c>
       <c r="AN3" t="n">
-        <v>17174763176510</v>
+        <v>14079202500510</v>
       </c>
       <c r="AO3" t="n">
-        <v>14049858342560</v>
+        <v>11360599604860</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>12904701642.74245</v>
+        <v>10967950997.25201</v>
       </c>
       <c r="C4" t="n">
-        <v>0.15154</v>
+        <v>0.234945</v>
       </c>
       <c r="D4" t="n">
-        <v>85157000000</v>
+        <v>46683000000</v>
       </c>
       <c r="E4" t="n">
-        <v>85157000000</v>
+        <v>46683000000</v>
       </c>
       <c r="F4" t="n">
-        <v>1030328630870</v>
+        <v>758479879640</v>
       </c>
       <c r="G4" t="n">
-        <v>253500000000</v>
+        <v>162205000000</v>
       </c>
       <c r="H4" t="n">
-        <v>1650837751600</v>
+        <v>1553048024760</v>
       </c>
       <c r="I4" t="n">
-        <v>-271305677000</v>
+        <v>-473411800000</v>
       </c>
       <c r="J4" t="n">
-        <v>271305677000</v>
+        <v>473411800000</v>
       </c>
       <c r="K4" t="n">
-        <v>4219288859890</v>
+        <v>3983930092550</v>
       </c>
       <c r="L4" t="n">
-        <v>958076332512.7424</v>
+        <v>722764830637.252</v>
       </c>
       <c r="M4" t="n">
-        <v>1030328630870</v>
+        <v>758479879640</v>
       </c>
       <c r="N4" t="n">
-        <v>12699670426020</v>
-      </c>
-      <c r="O4" t="n">
-        <v>5119000000</v>
-      </c>
+        <v>16095126952560</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>824922843</v>
+        <v>795052285</v>
       </c>
       <c r="Q4" t="n">
-        <v>824922843</v>
+        <v>795052285</v>
       </c>
       <c r="R4" t="n">
-        <v>1249</v>
+        <v>954</v>
       </c>
       <c r="S4" t="n">
-        <v>1249</v>
+        <v>954</v>
       </c>
       <c r="T4" t="n">
-        <v>1030328630870</v>
+        <v>758479879640</v>
       </c>
       <c r="U4" t="n">
-        <v>1030328630870</v>
+        <v>758479879640</v>
       </c>
       <c r="V4" t="n">
-        <v>-140148993360</v>
+        <v>-67500898620</v>
       </c>
       <c r="W4" t="n">
-        <v>1170477624230</v>
+        <v>825980778270</v>
       </c>
       <c r="X4" t="n">
-        <v>1170477624230</v>
+        <v>825980778270</v>
       </c>
       <c r="Y4" t="n">
-        <v>209054450360</v>
+        <v>253655446480</v>
       </c>
       <c r="Z4" t="n">
-        <v>1379532074600</v>
+        <v>1079636224760</v>
       </c>
       <c r="AA4" t="n">
-        <v>948652191560</v>
+        <v>1081664813150</v>
       </c>
       <c r="AB4" t="n">
-        <v>85157000000</v>
+        <v>46683000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-87405000000</v>
+        <v>-53722000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2248000000</v>
+        <v>7039000000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-271305677000</v>
+        <v>-473411800000</v>
       </c>
       <c r="AF4" t="n">
-        <v>271305677000</v>
+        <v>473411800000</v>
       </c>
       <c r="AG4" t="n">
-        <v>786612170480</v>
+        <v>1182527486350</v>
       </c>
       <c r="AH4" t="n">
-        <v>52992000000</v>
+        <v>77826000000</v>
       </c>
       <c r="AI4" t="n">
-        <v>52992000000</v>
+        <v>77826000000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>331243973680</v>
+        <v>349706323650</v>
       </c>
       <c r="AK4" t="n">
-        <v>331243973680</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>5119000000</v>
-      </c>
+        <v>349706323650</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>14079202500510</v>
+        <v>17174763176510</v>
       </c>
       <c r="AN4" t="n">
-        <v>14079202500510</v>
+        <v>17174763176510</v>
       </c>
       <c r="AO4" t="n">
-        <v>11360599604860</v>
+        <v>14049858342560</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>8077658433.431293</v>
+        <v>-5067301485.846427</v>
       </c>
       <c r="C5" t="n">
-        <v>0.246812</v>
+        <v>0.261714</v>
       </c>
       <c r="D5" t="n">
-        <v>32728000000</v>
+        <v>-19362000000</v>
       </c>
       <c r="E5" t="n">
-        <v>32728000000</v>
+        <v>-19362000000</v>
       </c>
       <c r="F5" t="n">
-        <v>1191311383170</v>
+        <v>737253509030</v>
       </c>
       <c r="G5" t="n">
-        <v>275814000000</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+        <v>195800000000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1667469897590</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-494481814000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>494481814000</v>
+      </c>
       <c r="K5" t="n">
-        <v>3628042437350</v>
+        <v>3974476131910</v>
       </c>
       <c r="L5" t="n">
-        <v>1166661041603.431</v>
+        <v>751548207544.1536</v>
       </c>
       <c r="M5" t="n">
-        <v>1191311383170</v>
+        <v>737253509030</v>
       </c>
       <c r="N5" t="n">
-        <v>19471829729240</v>
-      </c>
-      <c r="O5" t="n">
-        <v>12515000000</v>
-      </c>
+        <v>15483541484310</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>818770710</v>
+        <v>787664005</v>
       </c>
       <c r="Q5" t="n">
-        <v>818770710</v>
+        <v>757695274</v>
       </c>
       <c r="R5" t="n">
-        <v>1455</v>
+        <v>936</v>
       </c>
       <c r="S5" t="n">
-        <v>1455</v>
+        <v>936</v>
       </c>
       <c r="T5" t="n">
-        <v>1191311383170</v>
+        <v>737253509030</v>
       </c>
       <c r="U5" t="n">
-        <v>1191311383170</v>
+        <v>737253509030</v>
       </c>
       <c r="V5" t="n">
-        <v>-57848851760</v>
+        <v>-128747473070</v>
       </c>
       <c r="W5" t="n">
-        <v>1249160234930</v>
+        <v>866000982110</v>
       </c>
       <c r="X5" t="n">
-        <v>1249160234930</v>
+        <v>866000982110</v>
       </c>
       <c r="Y5" t="n">
-        <v>409336709560</v>
+        <v>306987101480</v>
       </c>
       <c r="Z5" t="n">
-        <v>1658496944490</v>
+        <v>1172988083590</v>
       </c>
       <c r="AA5" t="n">
-        <v>2039880662320</v>
+        <v>2830955223050</v>
       </c>
       <c r="AB5" t="n">
-        <v>32728000000</v>
+        <v>-19362000000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-34475000000</v>
+        <v>13182000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1747000000</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+        <v>6180000000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-494481814000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>494481814000</v>
+      </c>
       <c r="AG5" t="n">
-        <v>346425566570</v>
+        <v>1353915582660</v>
       </c>
       <c r="AH5" t="n">
-        <v>102749000000</v>
+        <v>83507000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>102749000000</v>
+        <v>83507000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>642608333890</v>
+        <v>389948006230</v>
       </c>
       <c r="AK5" t="n">
-        <v>642608333890</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>12515000000</v>
-      </c>
+        <v>389948006230</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>21130326673530</v>
+        <v>16656529568710</v>
       </c>
       <c r="AN5" t="n">
-        <v>21130326673530</v>
+        <v>16656529568710</v>
       </c>
       <c r="AO5" t="n">
-        <v>11594854561460</v>
+        <v>13211637081420</v>
       </c>
     </row>
   </sheetData>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>117139750</v>
@@ -1442,46 +1442,46 @@
         <v>868530000</v>
       </c>
       <c r="E2" t="n">
-        <v>8407102745750</v>
+        <v>4388081993730</v>
       </c>
       <c r="F2" t="n">
-        <v>13162378974750</v>
+        <v>6987337244000</v>
       </c>
       <c r="G2" t="n">
-        <v>11154184026790</v>
+        <v>10112053602590</v>
       </c>
       <c r="H2" t="n">
-        <v>24957235529540</v>
+        <v>18261185575950</v>
       </c>
       <c r="I2" t="n">
-        <v>11154184026790</v>
+        <v>10112053602590</v>
       </c>
       <c r="J2" t="n">
-        <v>11794856554790</v>
+        <v>11273848331950</v>
       </c>
       <c r="K2" t="n">
-        <v>24957235529540</v>
+        <v>18261185575950</v>
       </c>
       <c r="L2" t="n">
-        <v>14278000736710</v>
+        <v>13419581014660</v>
       </c>
       <c r="M2" t="n">
-        <v>2483144181910</v>
+        <v>2145732682700</v>
       </c>
       <c r="N2" t="n">
-        <v>11794856554790</v>
+        <v>11273848331950</v>
       </c>
       <c r="O2" t="n">
-        <v>1114575560310</v>
+        <v>2059180171770</v>
       </c>
       <c r="P2" t="n">
-        <v>368955000000</v>
+        <v>409349000000</v>
       </c>
       <c r="Q2" t="n">
-        <v>924085000000</v>
+        <v>924084825000</v>
       </c>
       <c r="R2" t="n">
-        <v>8205972926260</v>
+        <v>5083054481250</v>
       </c>
       <c r="S2" t="n">
         <v>485281042000</v>
@@ -1493,126 +1493,130 @@
         <v>4342650000000</v>
       </c>
       <c r="V2" t="n">
-        <v>145868430021350</v>
+        <v>150171792112670</v>
       </c>
       <c r="W2" t="n">
-        <v>4040619246000</v>
+        <v>989410715000</v>
       </c>
       <c r="X2" t="n">
-        <v>332932361000</v>
+        <v>287991084150</v>
       </c>
       <c r="Y2" t="n">
-        <v>747044000000</v>
+        <v>526829000000</v>
       </c>
       <c r="Z2" t="n">
-        <v>115627000000</v>
+        <v>62224000000</v>
       </c>
       <c r="AA2" t="n">
-        <v>736163790110</v>
+        <v>585246346250</v>
       </c>
       <c r="AB2" t="n">
-        <v>13162378974750</v>
+        <v>6987337244000</v>
       </c>
       <c r="AC2" t="n">
-        <v>13162378974750</v>
+        <v>6987337244000</v>
       </c>
       <c r="AD2" t="n">
-        <v>126995583000</v>
+        <v>89667427000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2470418063860</v>
+        <v>2554784735570</v>
       </c>
       <c r="AF2" t="n">
-        <v>645349000000</v>
+        <v>992370000000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1825069063860</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>1141786735570</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>420628000000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>160146430758070</v>
+        <v>163591373127330</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18807917000</v>
+        <v>25369067000</v>
       </c>
       <c r="AK2" t="n">
-        <v>94164335010</v>
+        <v>138927518550</v>
       </c>
       <c r="AL2" t="n">
-        <v>1106880910000</v>
+        <v>181065509000</v>
       </c>
       <c r="AM2" t="n">
-        <v>124632636288650</v>
+        <v>91692295698270</v>
       </c>
       <c r="AN2" t="n">
-        <v>13315438959000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>12208558049000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
+        <v>183523509000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>2458000000</v>
+      </c>
       <c r="AQ2" t="n">
-        <v>451874531880</v>
+        <v>367916057180</v>
       </c>
       <c r="AR2" t="n">
-        <v>451874531880</v>
+        <v>367916057000</v>
       </c>
       <c r="AS2" t="n">
-        <v>2430233956000</v>
+        <v>2497974077000</v>
       </c>
       <c r="AT2" t="n">
-        <v>640672528000</v>
+        <v>1161794729360</v>
       </c>
       <c r="AU2" t="n">
-        <v>427875528000</v>
+        <v>1147002729360</v>
       </c>
       <c r="AV2" t="n">
-        <v>212797000000</v>
+        <v>14792000000</v>
       </c>
       <c r="AW2" t="n">
-        <v>2089404488490</v>
+        <v>1884292428000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-1129981000000</v>
+        <v>-861376000000</v>
       </c>
       <c r="AY2" t="n">
-        <v>3219385488000</v>
+        <v>2745668428000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>64683000000</v>
+        <v>2061000000</v>
       </c>
       <c r="BA2" t="n">
-        <v>462869488000</v>
+        <v>20953428000</v>
       </c>
       <c r="BB2" t="n">
-        <v>513700000000</v>
+        <v>429183000000</v>
       </c>
       <c r="BC2" t="n">
-        <v>1242230000000</v>
+        <v>1360158000000</v>
       </c>
       <c r="BD2" t="n">
-        <v>935903000000</v>
+        <v>933313000000</v>
       </c>
       <c r="BE2" t="n">
-        <v>470266692180</v>
+        <v>310990406260</v>
       </c>
       <c r="BF2" t="n">
-        <v>2323055000000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
+        <v>2142618000000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>412185000000</v>
+      </c>
       <c r="BH2" t="n">
-        <v>115620599026770</v>
+        <v>93740111382360</v>
       </c>
       <c r="BI2" t="n">
-        <v>110865322797770</v>
+        <v>91140856132090</v>
       </c>
       <c r="BJ2" t="n">
-        <v>4755276229000</v>
+        <v>2599255250270</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>117139750</v>
@@ -1624,46 +1628,46 @@
         <v>868530000</v>
       </c>
       <c r="E3" t="n">
-        <v>5714217329560</v>
+        <v>5081159095170</v>
       </c>
       <c r="F3" t="n">
-        <v>10982132757560</v>
+        <v>9848429543170</v>
       </c>
       <c r="G3" t="n">
-        <v>12415073775190</v>
+        <v>17046457001520</v>
       </c>
       <c r="H3" t="n">
-        <v>24020303906750</v>
+        <v>27220433311120</v>
       </c>
       <c r="I3" t="n">
-        <v>12415073775190</v>
+        <v>17046457001520</v>
       </c>
       <c r="J3" t="n">
-        <v>13038171149190</v>
+        <v>17372003767950</v>
       </c>
       <c r="K3" t="n">
-        <v>24020303906750</v>
+        <v>27220433311120</v>
       </c>
       <c r="L3" t="n">
-        <v>15475087526210</v>
+        <v>19694680831180</v>
       </c>
       <c r="M3" t="n">
-        <v>2436916377010</v>
+        <v>2322677063220</v>
       </c>
       <c r="N3" t="n">
-        <v>13038171149190</v>
+        <v>17372003767950</v>
       </c>
       <c r="O3" t="n">
-        <v>508932801130</v>
+        <v>1564764078440</v>
       </c>
       <c r="P3" t="n">
-        <v>367512000000</v>
+        <v>401432000000</v>
       </c>
       <c r="Q3" t="n">
         <v>924085000000</v>
       </c>
       <c r="R3" t="n">
-        <v>7609770819910</v>
+        <v>7929008536430</v>
       </c>
       <c r="S3" t="n">
         <v>485281042000</v>
@@ -1675,128 +1679,132 @@
         <v>4342650000000</v>
       </c>
       <c r="V3" t="n">
-        <v>132426755373730</v>
+        <v>126615799732830</v>
       </c>
       <c r="W3" t="n">
-        <v>3035481183000</v>
+        <v>4789164053000</v>
       </c>
       <c r="X3" t="n">
-        <v>318667794000</v>
+        <v>256223857000</v>
       </c>
       <c r="Y3" t="n">
-        <v>597756000000</v>
+        <v>590336000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>175794000000</v>
+        <v>61039000000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1361035995220</v>
+        <v>2364019316400</v>
       </c>
       <c r="AB3" t="n">
-        <v>10982132757560</v>
+        <v>9848429543170</v>
       </c>
       <c r="AC3" t="n">
-        <v>10982132757560</v>
+        <v>9848429543170</v>
       </c>
       <c r="AD3" t="n">
-        <v>122265775000</v>
+        <v>125570590000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2157275914730</v>
+        <v>1379105603880</v>
       </c>
       <c r="AF3" t="n">
-        <v>979845000000</v>
+        <v>574078000000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1177430914730</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>805027603880</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>476381000000</v>
+      </c>
       <c r="AI3" t="n">
-        <v>147901842899940</v>
+        <v>146310480564010</v>
       </c>
       <c r="AJ3" t="n">
-        <v>58699378000</v>
+        <v>35721695000</v>
       </c>
       <c r="AK3" t="n">
-        <v>52789166270</v>
+        <v>22700355250</v>
       </c>
       <c r="AL3" t="n">
-        <v>853851830000</v>
+        <v>1007942283000</v>
       </c>
       <c r="AM3" t="n">
-        <v>110564209050630</v>
+        <v>107327774647990</v>
       </c>
       <c r="AN3" t="n">
-        <v>12815052071000</v>
+        <v>32904004296240</v>
       </c>
       <c r="AO3" t="n">
-        <v>11961200241000</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>31896062013240</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2200000000</v>
+      </c>
       <c r="AQ3" t="n">
-        <v>602098682490</v>
+        <v>537516486000</v>
       </c>
       <c r="AR3" t="n">
-        <v>602098682490</v>
+        <v>537516486000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2587129933000</v>
+        <v>2701400824000</v>
       </c>
       <c r="AT3" t="n">
-        <v>623097374000</v>
+        <v>325546766430</v>
       </c>
       <c r="AU3" t="n">
-        <v>430994374000</v>
+        <v>310754766430</v>
       </c>
       <c r="AV3" t="n">
-        <v>192103000000</v>
+        <v>14792000000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1821844947310</v>
+        <v>1804134233040</v>
       </c>
       <c r="AX3" t="n">
-        <v>-1034301000000</v>
+        <v>-920287000000</v>
       </c>
       <c r="AY3" t="n">
-        <v>2856145947000</v>
+        <v>2724421233000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>27160000000</v>
+        <v>5140000000</v>
       </c>
       <c r="BA3" t="n">
-        <v>428438947000</v>
+        <v>333563233000</v>
       </c>
       <c r="BB3" t="n">
-        <v>463855000000</v>
+        <v>430732000000</v>
       </c>
       <c r="BC3" t="n">
-        <v>1183673000000</v>
+        <v>1196241000000</v>
       </c>
       <c r="BD3" t="n">
-        <v>753019000000</v>
+        <v>758745000000</v>
       </c>
       <c r="BE3" t="n">
-        <v>525237379660</v>
+        <v>357343112970</v>
       </c>
       <c r="BF3" t="n">
-        <v>2496019000000</v>
+        <v>2107457550000</v>
       </c>
       <c r="BG3" t="n">
-        <v>41155000</v>
+        <v>10444980000</v>
       </c>
       <c r="BH3" t="n">
-        <v>102414973725140</v>
+        <v>78653524313750</v>
       </c>
       <c r="BI3" t="n">
-        <v>97147058297140</v>
+        <v>73886253865750</v>
       </c>
       <c r="BJ3" t="n">
-        <v>5267915428000</v>
+        <v>4767270448000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>117139750</v>
@@ -1808,46 +1816,46 @@
         <v>868530000</v>
       </c>
       <c r="E4" t="n">
-        <v>5081159095170</v>
+        <v>5714217329560</v>
       </c>
       <c r="F4" t="n">
-        <v>9848429543170</v>
+        <v>10982132757560</v>
       </c>
       <c r="G4" t="n">
-        <v>17046457001520</v>
+        <v>12415073775190</v>
       </c>
       <c r="H4" t="n">
-        <v>27220433311120</v>
+        <v>24020303906750</v>
       </c>
       <c r="I4" t="n">
-        <v>17046457001520</v>
+        <v>12415073775190</v>
       </c>
       <c r="J4" t="n">
-        <v>17372003767950</v>
+        <v>13038171149190</v>
       </c>
       <c r="K4" t="n">
-        <v>27220433311120</v>
+        <v>24020303906750</v>
       </c>
       <c r="L4" t="n">
-        <v>19694680831180</v>
+        <v>15475087526210</v>
       </c>
       <c r="M4" t="n">
-        <v>2322677063220</v>
+        <v>2436916377010</v>
       </c>
       <c r="N4" t="n">
-        <v>17372003767950</v>
+        <v>13038171149190</v>
       </c>
       <c r="O4" t="n">
-        <v>1564764078440</v>
+        <v>508932801130</v>
       </c>
       <c r="P4" t="n">
-        <v>401432000000</v>
+        <v>367512000000</v>
       </c>
       <c r="Q4" t="n">
         <v>924085000000</v>
       </c>
       <c r="R4" t="n">
-        <v>7929008536430</v>
+        <v>7609770819910</v>
       </c>
       <c r="S4" t="n">
         <v>485281042000</v>
@@ -1859,132 +1867,128 @@
         <v>4342650000000</v>
       </c>
       <c r="V4" t="n">
-        <v>126615799732830</v>
+        <v>132426755373730</v>
       </c>
       <c r="W4" t="n">
-        <v>4789164053000</v>
+        <v>3035481183000</v>
       </c>
       <c r="X4" t="n">
-        <v>256223857000</v>
+        <v>318667794000</v>
       </c>
       <c r="Y4" t="n">
-        <v>590336000000</v>
+        <v>597756000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>61039000000</v>
+        <v>175794000000</v>
       </c>
       <c r="AA4" t="n">
-        <v>2364019316400</v>
+        <v>1361035995220</v>
       </c>
       <c r="AB4" t="n">
-        <v>9848429543170</v>
+        <v>10982132757560</v>
       </c>
       <c r="AC4" t="n">
-        <v>9848429543170</v>
+        <v>10982132757560</v>
       </c>
       <c r="AD4" t="n">
-        <v>125570590000</v>
+        <v>122265775000</v>
       </c>
       <c r="AE4" t="n">
-        <v>1379105603880</v>
+        <v>2157275914730</v>
       </c>
       <c r="AF4" t="n">
-        <v>574078000000</v>
+        <v>979845000000</v>
       </c>
       <c r="AG4" t="n">
-        <v>805027603880</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>476381000000</v>
-      </c>
+        <v>1177430914730</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>146310480564010</v>
+        <v>147901842899940</v>
       </c>
       <c r="AJ4" t="n">
-        <v>35721695000</v>
+        <v>58699378000</v>
       </c>
       <c r="AK4" t="n">
-        <v>22700355250</v>
+        <v>52789166270</v>
       </c>
       <c r="AL4" t="n">
-        <v>1007942283000</v>
+        <v>853851830000</v>
       </c>
       <c r="AM4" t="n">
-        <v>107327774647990</v>
+        <v>110564209050630</v>
       </c>
       <c r="AN4" t="n">
-        <v>32904004296240</v>
+        <v>12815052071000</v>
       </c>
       <c r="AO4" t="n">
-        <v>31896062013240</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2200000000</v>
-      </c>
+        <v>11961200241000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
-        <v>537516486000</v>
+        <v>602098682490</v>
       </c>
       <c r="AR4" t="n">
-        <v>537516486000</v>
+        <v>602098682490</v>
       </c>
       <c r="AS4" t="n">
-        <v>2701400824000</v>
+        <v>2587129933000</v>
       </c>
       <c r="AT4" t="n">
-        <v>325546766430</v>
+        <v>623097374000</v>
       </c>
       <c r="AU4" t="n">
-        <v>310754766430</v>
+        <v>430994374000</v>
       </c>
       <c r="AV4" t="n">
-        <v>14792000000</v>
+        <v>192103000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1804134233040</v>
+        <v>1821844947310</v>
       </c>
       <c r="AX4" t="n">
-        <v>-920287000000</v>
+        <v>-1034301000000</v>
       </c>
       <c r="AY4" t="n">
-        <v>2724421233000</v>
+        <v>2856145947000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5140000000</v>
+        <v>27160000000</v>
       </c>
       <c r="BA4" t="n">
-        <v>333563233000</v>
+        <v>428438947000</v>
       </c>
       <c r="BB4" t="n">
-        <v>430732000000</v>
+        <v>463855000000</v>
       </c>
       <c r="BC4" t="n">
-        <v>1196241000000</v>
+        <v>1183673000000</v>
       </c>
       <c r="BD4" t="n">
-        <v>758745000000</v>
+        <v>753019000000</v>
       </c>
       <c r="BE4" t="n">
-        <v>357343112970</v>
+        <v>525237379660</v>
       </c>
       <c r="BF4" t="n">
-        <v>2107457550000</v>
+        <v>2496019000000</v>
       </c>
       <c r="BG4" t="n">
-        <v>10444980000</v>
+        <v>41155000</v>
       </c>
       <c r="BH4" t="n">
-        <v>78653524313750</v>
+        <v>102414973725140</v>
       </c>
       <c r="BI4" t="n">
-        <v>73886253865750</v>
+        <v>97147058297140</v>
       </c>
       <c r="BJ4" t="n">
-        <v>4767270448000</v>
+        <v>5267915428000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>117139750</v>
@@ -1996,46 +2000,46 @@
         <v>868530000</v>
       </c>
       <c r="E5" t="n">
-        <v>4388081993730</v>
+        <v>8407102745750</v>
       </c>
       <c r="F5" t="n">
-        <v>6987337244000</v>
+        <v>13162378974750</v>
       </c>
       <c r="G5" t="n">
-        <v>10112053602590</v>
+        <v>11154184026790</v>
       </c>
       <c r="H5" t="n">
-        <v>18261185575950</v>
+        <v>24957235529540</v>
       </c>
       <c r="I5" t="n">
-        <v>10112053602590</v>
+        <v>11154184026790</v>
       </c>
       <c r="J5" t="n">
-        <v>11273848331950</v>
+        <v>11794856554790</v>
       </c>
       <c r="K5" t="n">
-        <v>18261185575950</v>
+        <v>24957235529540</v>
       </c>
       <c r="L5" t="n">
-        <v>13419581014660</v>
+        <v>14278000736710</v>
       </c>
       <c r="M5" t="n">
-        <v>2145732682700</v>
+        <v>2483144181910</v>
       </c>
       <c r="N5" t="n">
-        <v>11273848331950</v>
+        <v>11794856554790</v>
       </c>
       <c r="O5" t="n">
-        <v>2059180171770</v>
+        <v>1114575560310</v>
       </c>
       <c r="P5" t="n">
-        <v>409349000000</v>
+        <v>368955000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>924084825000</v>
+        <v>924085000000</v>
       </c>
       <c r="R5" t="n">
-        <v>5083054481250</v>
+        <v>8205972926260</v>
       </c>
       <c r="S5" t="n">
         <v>485281042000</v>
@@ -2047,125 +2051,121 @@
         <v>4342650000000</v>
       </c>
       <c r="V5" t="n">
-        <v>150171792112670</v>
+        <v>145868430021350</v>
       </c>
       <c r="W5" t="n">
-        <v>989410715000</v>
+        <v>4040619246000</v>
       </c>
       <c r="X5" t="n">
-        <v>287991084150</v>
+        <v>332932361000</v>
       </c>
       <c r="Y5" t="n">
-        <v>526829000000</v>
+        <v>747044000000</v>
       </c>
       <c r="Z5" t="n">
-        <v>62224000000</v>
+        <v>115627000000</v>
       </c>
       <c r="AA5" t="n">
-        <v>585246346250</v>
+        <v>736163790110</v>
       </c>
       <c r="AB5" t="n">
-        <v>6987337244000</v>
+        <v>13162378974750</v>
       </c>
       <c r="AC5" t="n">
-        <v>6987337244000</v>
+        <v>13162378974750</v>
       </c>
       <c r="AD5" t="n">
-        <v>89667427000</v>
+        <v>126995583000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2554784735570</v>
+        <v>2470418063860</v>
       </c>
       <c r="AF5" t="n">
-        <v>992370000000</v>
+        <v>645349000000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1141786735570</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>420628000000</v>
-      </c>
+        <v>1825069063860</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>163591373127330</v>
+        <v>160146430758070</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25369067000</v>
+        <v>18807917000</v>
       </c>
       <c r="AK5" t="n">
-        <v>138927518550</v>
+        <v>94164335010</v>
       </c>
       <c r="AL5" t="n">
-        <v>181065509000</v>
+        <v>1106880910000</v>
       </c>
       <c r="AM5" t="n">
-        <v>91692295698270</v>
+        <v>124632636288650</v>
       </c>
       <c r="AN5" t="n">
-        <v>183523509000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="n">
-        <v>2458000000</v>
-      </c>
+        <v>13315438959000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>12208558049000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
-        <v>367916057180</v>
+        <v>451874531880</v>
       </c>
       <c r="AR5" t="n">
-        <v>367916057000</v>
+        <v>451874531880</v>
       </c>
       <c r="AS5" t="n">
-        <v>2497974077000</v>
+        <v>2430233956000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1161794729360</v>
+        <v>640672528000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1147002729360</v>
+        <v>427875528000</v>
       </c>
       <c r="AV5" t="n">
-        <v>14792000000</v>
+        <v>212797000000</v>
       </c>
       <c r="AW5" t="n">
-        <v>1884292428000</v>
+        <v>2089404488490</v>
       </c>
       <c r="AX5" t="n">
-        <v>-861376000000</v>
+        <v>-1129981000000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2745668428000</v>
+        <v>3219385488000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2061000000</v>
+        <v>64683000000</v>
       </c>
       <c r="BA5" t="n">
-        <v>20953428000</v>
+        <v>462869488000</v>
       </c>
       <c r="BB5" t="n">
-        <v>429183000000</v>
+        <v>513700000000</v>
       </c>
       <c r="BC5" t="n">
-        <v>1360158000000</v>
+        <v>1242230000000</v>
       </c>
       <c r="BD5" t="n">
-        <v>933313000000</v>
+        <v>935903000000</v>
       </c>
       <c r="BE5" t="n">
-        <v>310990406260</v>
+        <v>470266692180</v>
       </c>
       <c r="BF5" t="n">
-        <v>2142618000000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>412185000000</v>
-      </c>
+        <v>2323055000000</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>93740111382360</v>
+        <v>115620599026770</v>
       </c>
       <c r="BI5" t="n">
-        <v>91140856132090</v>
+        <v>110865322797770</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2599255250270</v>
+        <v>4755276229000</v>
       </c>
     </row>
   </sheetData>
@@ -2456,662 +2456,662 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>5115160276290</v>
+        <v>5452018963190</v>
       </c>
       <c r="C2" t="n">
-        <v>-704363093340</v>
+        <v>-1874094291390</v>
       </c>
       <c r="D2" t="n">
-        <v>2741077741040</v>
+        <v>2751247334570</v>
       </c>
       <c r="E2" t="n">
-        <v>-313415027920</v>
+        <v>-108966640570</v>
       </c>
       <c r="F2" t="n">
-        <v>2438417229130</v>
+        <v>1336123701790</v>
       </c>
       <c r="G2" t="n">
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>3670919427820</v>
+        <v>1051931381290</v>
       </c>
       <c r="I2" t="n">
-        <v>8601825670</v>
+        <v>2941766100</v>
       </c>
       <c r="J2" t="n">
-        <v>-1241104024370</v>
+        <v>281250554390</v>
       </c>
       <c r="K2" t="n">
-        <v>2402622926450</v>
+        <v>151635672540</v>
       </c>
       <c r="L2" t="n">
-        <v>505704864190</v>
+        <v>-612337963140</v>
       </c>
       <c r="M2" t="n">
-        <v>-139796585440</v>
+        <v>-113179407500</v>
       </c>
       <c r="N2" t="n">
-        <v>-139796585440</v>
+        <v>-113179407500</v>
       </c>
       <c r="O2" t="n">
-        <v>2036714647700</v>
+        <v>877153043180</v>
       </c>
       <c r="P2" t="n">
-        <v>2036714647700</v>
+        <v>877153043180</v>
       </c>
       <c r="Q2" t="n">
-        <v>-704363093340</v>
+        <v>-1874094291390</v>
       </c>
       <c r="R2" t="n">
-        <v>2741077741040</v>
+        <v>2751247334570</v>
       </c>
       <c r="S2" t="n">
-        <v>-9072302255030</v>
+        <v>-5431370721910</v>
       </c>
       <c r="T2" t="n">
-        <v>-935408160</v>
+        <v>-3004978140</v>
       </c>
       <c r="U2" t="n">
-        <v>13850784000</v>
+        <v>12021315830</v>
       </c>
       <c r="V2" t="n">
-        <v>-8674222881110</v>
+        <v>-5318553080630</v>
       </c>
       <c r="W2" t="n">
-        <v>28732441328210</v>
+        <v>9097286360650</v>
       </c>
       <c r="X2" t="n">
-        <v>-37406664209320</v>
+        <v>-14415839441280</v>
       </c>
       <c r="Y2" t="n">
-        <v>34543505400</v>
+        <v>24587523880</v>
       </c>
       <c r="Z2" t="n">
-        <v>581909436060</v>
+        <v>113230681480</v>
       </c>
       <c r="AA2" t="n">
-        <v>-547365930660</v>
+        <v>-88643157600</v>
       </c>
       <c r="AB2" t="n">
-        <v>-176443041530</v>
+        <v>-57437774070</v>
       </c>
       <c r="AC2" t="n">
-        <v>133802054360</v>
+        <v>178716952300</v>
       </c>
       <c r="AD2" t="n">
-        <v>-310245095890</v>
+        <v>-236154726370</v>
       </c>
       <c r="AE2" t="n">
-        <v>-83376181800</v>
+        <v>-88983728780</v>
       </c>
       <c r="AF2" t="n">
-        <v>24465587490</v>
+        <v>19982911790</v>
       </c>
       <c r="AG2" t="n">
-        <v>-107841769290</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-185719031830</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>19854226800</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-205573258630</v>
-      </c>
+        <v>-108966640570</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
-        <v>5428575304210</v>
+        <v>5560985603760</v>
       </c>
       <c r="AL2" t="n">
-        <v>-233142680</v>
+        <v>-33285370920</v>
       </c>
       <c r="AM2" t="n">
-        <v>3160306835520</v>
+        <v>2908259177730</v>
       </c>
       <c r="AN2" t="n">
-        <v>-500756954410</v>
+        <v>-59169145480</v>
       </c>
       <c r="AO2" t="n">
-        <v>1047380007100</v>
+        <v>614704984410</v>
       </c>
       <c r="AP2" t="n">
-        <v>1882951736260</v>
+        <v>-643084722140</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-481175000000</v>
+        <v>5758000000</v>
       </c>
       <c r="AR2" t="n">
-        <v>668442736000</v>
+        <v>-611345722000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-589014160000</v>
+        <v>-3284042555000</v>
       </c>
       <c r="AT2" t="n">
-        <v>15569000000</v>
+        <v>7628000000</v>
       </c>
       <c r="AU2" t="n">
-        <v>226589000000</v>
+        <v>4408755000000</v>
       </c>
       <c r="AV2" t="n">
-        <v>195800000000</v>
+        <v>275814000000</v>
       </c>
       <c r="AW2" t="n">
-        <v>83507000000</v>
+        <v>102760000000</v>
       </c>
       <c r="AX2" t="n">
-        <v>112293000000</v>
+        <v>173054000000</v>
       </c>
       <c r="AY2" t="n">
-        <v>39142000000</v>
+        <v>43707000000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1281559000000</v>
+        <v>1658687000000</v>
       </c>
       <c r="BA2" t="n">
-        <v>-2119335000000</v>
+        <v>-1503165000000</v>
       </c>
       <c r="BB2" t="n">
-        <v>-8074000000</v>
+        <v>-41945000000</v>
       </c>
       <c r="BC2" t="n">
-        <v>866000982110</v>
+        <v>1249160234930</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1599706866660</v>
+        <v>1052386497540</v>
       </c>
       <c r="C3" t="n">
-        <v>-780976968660</v>
+        <v>-7088585176050</v>
       </c>
       <c r="D3" t="n">
-        <v>1899691828430</v>
+        <v>8464793043410</v>
       </c>
       <c r="E3" t="n">
-        <v>-138262363350</v>
+        <v>-136151714420</v>
       </c>
       <c r="F3" t="n">
-        <v>3670919427820</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-20</v>
-      </c>
+        <v>2902135448280</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>2902135448280</v>
+        <v>2044657688940</v>
       </c>
       <c r="I3" t="n">
-        <v>-2496842000</v>
+        <v>-8049682620</v>
       </c>
       <c r="J3" t="n">
-        <v>771280821560</v>
+        <v>865527441960</v>
       </c>
       <c r="K3" t="n">
-        <v>-125288902150</v>
+        <v>1064458460930</v>
       </c>
       <c r="L3" t="n">
-        <v>-1194355161920</v>
+        <v>-219081289310</v>
       </c>
       <c r="M3" t="n">
-        <v>-49648600000</v>
+        <v>-92668117120</v>
       </c>
       <c r="N3" t="n">
-        <v>-49648600000</v>
+        <v>-92668117120</v>
       </c>
       <c r="O3" t="n">
-        <v>1118714859770</v>
+        <v>1376207867360</v>
       </c>
       <c r="P3" t="n">
-        <v>1118714859770</v>
+        <v>1376207867360</v>
       </c>
       <c r="Q3" t="n">
-        <v>-780976968660</v>
+        <v>-7088585176050</v>
       </c>
       <c r="R3" t="n">
-        <v>1899691828430</v>
+        <v>8464793043410</v>
       </c>
       <c r="S3" t="n">
-        <v>-841399506300</v>
+        <v>-1387469230930</v>
       </c>
       <c r="T3" t="n">
-        <v>3496449840</v>
+        <v>-38138984730</v>
       </c>
       <c r="U3" t="n">
-        <v>5546028000</v>
+        <v>7402841000</v>
       </c>
       <c r="V3" t="n">
-        <v>-507379463710</v>
+        <v>-1134993329650</v>
       </c>
       <c r="W3" t="n">
-        <v>33021673278900</v>
+        <v>11334806832680</v>
       </c>
       <c r="X3" t="n">
-        <v>-33529052742610</v>
+        <v>-12469800162330</v>
       </c>
       <c r="Y3" t="n">
-        <v>186531123700</v>
+        <v>21633789130</v>
       </c>
       <c r="Z3" t="n">
-        <v>186758579090</v>
+        <v>268834608150</v>
       </c>
       <c r="AA3" t="n">
-        <v>-227455390</v>
+        <v>-247200819020</v>
       </c>
       <c r="AB3" t="n">
-        <v>-392811164660</v>
+        <v>-225356146550</v>
       </c>
       <c r="AC3" t="n">
-        <v>159390676690</v>
+        <v>27038172860</v>
       </c>
       <c r="AD3" t="n">
-        <v>-552201841350</v>
+        <v>-252394319410</v>
       </c>
       <c r="AE3" t="n">
-        <v>-100984083540</v>
+        <v>-45096500610</v>
       </c>
       <c r="AF3" t="n">
-        <v>295166470</v>
+        <v>13754143600</v>
       </c>
       <c r="AG3" t="n">
-        <v>-101279250010</v>
+        <v>-58850644210</v>
       </c>
       <c r="AH3" t="n">
-        <v>-35798395930</v>
+        <v>27079100480</v>
       </c>
       <c r="AI3" t="n">
-        <v>1184717410</v>
+        <v>104380170690</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-36983113340</v>
+        <v>-77301070210</v>
       </c>
       <c r="AK3" t="n">
-        <v>1737969230010</v>
+        <v>1188538211960</v>
       </c>
       <c r="AL3" t="n">
-        <v>-117224494100</v>
+        <v>-301269503210</v>
       </c>
       <c r="AM3" t="n">
-        <v>3365229826320</v>
+        <v>3123674547470</v>
       </c>
       <c r="AN3" t="n">
-        <v>-471401552840</v>
+        <v>-279232313080</v>
       </c>
       <c r="AO3" t="n">
-        <v>832720636580</v>
+        <v>808010665750</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1684446100670</v>
+        <v>-1980419774160</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-757874000000</v>
+        <v>-623035000000</v>
       </c>
       <c r="AR3" t="n">
-        <v>2244635899000</v>
+        <v>-891358774000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-871091863000</v>
+        <v>-2097001035000</v>
       </c>
       <c r="AT3" t="n">
-        <v>10349000000</v>
+        <v>7396000000</v>
       </c>
       <c r="AU3" t="n">
-        <v>148670000000</v>
+        <v>2248000000</v>
       </c>
       <c r="AV3" t="n">
-        <v>162205000000</v>
+        <v>253500000000</v>
       </c>
       <c r="AW3" t="n">
-        <v>77826000000</v>
+        <v>55635000000</v>
       </c>
       <c r="AX3" t="n">
-        <v>84379000000</v>
+        <v>197865000000</v>
       </c>
       <c r="AY3" t="n">
-        <v>45649000000</v>
+        <v>54215000000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>48186000000</v>
+        <v>1174346000000</v>
       </c>
       <c r="BA3" t="n">
-        <v>-502326000000</v>
+        <v>-740967000000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-63011000000</v>
+        <v>-93061000000</v>
       </c>
       <c r="BC3" t="n">
-        <v>825980778270</v>
+        <v>1170477624230</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1052386497540</v>
+        <v>1599706866660</v>
       </c>
       <c r="C4" t="n">
-        <v>-7088585176050</v>
+        <v>-780976968660</v>
       </c>
       <c r="D4" t="n">
-        <v>8464793043410</v>
+        <v>1899691828430</v>
       </c>
       <c r="E4" t="n">
-        <v>-136151714420</v>
+        <v>-138262363350</v>
       </c>
       <c r="F4" t="n">
+        <v>3670919427820</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="H4" t="n">
         <v>2902135448280</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>2044657688940</v>
-      </c>
       <c r="I4" t="n">
-        <v>-8049682620</v>
+        <v>-2496842000</v>
       </c>
       <c r="J4" t="n">
-        <v>865527441960</v>
+        <v>771280821560</v>
       </c>
       <c r="K4" t="n">
-        <v>1064458460930</v>
+        <v>-125288902150</v>
       </c>
       <c r="L4" t="n">
-        <v>-219081289310</v>
+        <v>-1194355161920</v>
       </c>
       <c r="M4" t="n">
-        <v>-92668117120</v>
+        <v>-49648600000</v>
       </c>
       <c r="N4" t="n">
-        <v>-92668117120</v>
+        <v>-49648600000</v>
       </c>
       <c r="O4" t="n">
-        <v>1376207867360</v>
+        <v>1118714859770</v>
       </c>
       <c r="P4" t="n">
-        <v>1376207867360</v>
+        <v>1118714859770</v>
       </c>
       <c r="Q4" t="n">
-        <v>-7088585176050</v>
+        <v>-780976968660</v>
       </c>
       <c r="R4" t="n">
-        <v>8464793043410</v>
+        <v>1899691828430</v>
       </c>
       <c r="S4" t="n">
-        <v>-1387469230930</v>
+        <v>-841399506300</v>
       </c>
       <c r="T4" t="n">
-        <v>-38138984730</v>
+        <v>3496449840</v>
       </c>
       <c r="U4" t="n">
-        <v>7402841000</v>
+        <v>5546028000</v>
       </c>
       <c r="V4" t="n">
-        <v>-1134993329650</v>
+        <v>-507379463710</v>
       </c>
       <c r="W4" t="n">
-        <v>11334806832680</v>
+        <v>33021673278900</v>
       </c>
       <c r="X4" t="n">
-        <v>-12469800162330</v>
+        <v>-33529052742610</v>
       </c>
       <c r="Y4" t="n">
-        <v>21633789130</v>
+        <v>186531123700</v>
       </c>
       <c r="Z4" t="n">
-        <v>268834608150</v>
+        <v>186758579090</v>
       </c>
       <c r="AA4" t="n">
-        <v>-247200819020</v>
+        <v>-227455390</v>
       </c>
       <c r="AB4" t="n">
-        <v>-225356146550</v>
+        <v>-392811164660</v>
       </c>
       <c r="AC4" t="n">
-        <v>27038172860</v>
+        <v>159390676690</v>
       </c>
       <c r="AD4" t="n">
-        <v>-252394319410</v>
+        <v>-552201841350</v>
       </c>
       <c r="AE4" t="n">
-        <v>-45096500610</v>
+        <v>-100984083540</v>
       </c>
       <c r="AF4" t="n">
-        <v>13754143600</v>
+        <v>295166470</v>
       </c>
       <c r="AG4" t="n">
-        <v>-58850644210</v>
+        <v>-101279250010</v>
       </c>
       <c r="AH4" t="n">
-        <v>27079100480</v>
+        <v>-35798395930</v>
       </c>
       <c r="AI4" t="n">
-        <v>104380170690</v>
+        <v>1184717410</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-77301070210</v>
+        <v>-36983113340</v>
       </c>
       <c r="AK4" t="n">
-        <v>1188538211960</v>
+        <v>1737969230010</v>
       </c>
       <c r="AL4" t="n">
-        <v>-301269503210</v>
+        <v>-117224494100</v>
       </c>
       <c r="AM4" t="n">
-        <v>3123674547470</v>
+        <v>3365229826320</v>
       </c>
       <c r="AN4" t="n">
-        <v>-279232313080</v>
+        <v>-471401552840</v>
       </c>
       <c r="AO4" t="n">
-        <v>808010665750</v>
+        <v>832720636580</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1980419774160</v>
+        <v>-1684446100670</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-623035000000</v>
+        <v>-757874000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-891358774000</v>
+        <v>2244635899000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-2097001035000</v>
+        <v>-871091863000</v>
       </c>
       <c r="AT4" t="n">
-        <v>7396000000</v>
+        <v>10349000000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2248000000</v>
+        <v>148670000000</v>
       </c>
       <c r="AV4" t="n">
-        <v>253500000000</v>
+        <v>162205000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>55635000000</v>
+        <v>77826000000</v>
       </c>
       <c r="AX4" t="n">
-        <v>197865000000</v>
+        <v>84379000000</v>
       </c>
       <c r="AY4" t="n">
-        <v>54215000000</v>
+        <v>45649000000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1174346000000</v>
+        <v>48186000000</v>
       </c>
       <c r="BA4" t="n">
-        <v>-740967000000</v>
+        <v>-502326000000</v>
       </c>
       <c r="BB4" t="n">
-        <v>-93061000000</v>
+        <v>-63011000000</v>
       </c>
       <c r="BC4" t="n">
-        <v>1170477624230</v>
+        <v>825980778270</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>5452018963190</v>
+        <v>5115160276290</v>
       </c>
       <c r="C5" t="n">
-        <v>-1874094291390</v>
+        <v>-704363093340</v>
       </c>
       <c r="D5" t="n">
-        <v>2751247334570</v>
+        <v>2741077741040</v>
       </c>
       <c r="E5" t="n">
-        <v>-108966640570</v>
+        <v>-313415027920</v>
       </c>
       <c r="F5" t="n">
-        <v>1336123701790</v>
+        <v>2438417229130</v>
       </c>
       <c r="G5" t="n">
         <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>1051931381290</v>
+        <v>3670919427820</v>
       </c>
       <c r="I5" t="n">
-        <v>2941766100</v>
+        <v>8601825670</v>
       </c>
       <c r="J5" t="n">
-        <v>281250554390</v>
+        <v>-1241104024370</v>
       </c>
       <c r="K5" t="n">
-        <v>151635672540</v>
+        <v>2402622926450</v>
       </c>
       <c r="L5" t="n">
-        <v>-612337963140</v>
+        <v>505704864190</v>
       </c>
       <c r="M5" t="n">
-        <v>-113179407500</v>
+        <v>-139796585440</v>
       </c>
       <c r="N5" t="n">
-        <v>-113179407500</v>
+        <v>-139796585440</v>
       </c>
       <c r="O5" t="n">
-        <v>877153043180</v>
+        <v>2036714647700</v>
       </c>
       <c r="P5" t="n">
-        <v>877153043180</v>
+        <v>2036714647700</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1874094291390</v>
+        <v>-704363093340</v>
       </c>
       <c r="R5" t="n">
-        <v>2751247334570</v>
+        <v>2741077741040</v>
       </c>
       <c r="S5" t="n">
-        <v>-5431370721910</v>
+        <v>-9072302255030</v>
       </c>
       <c r="T5" t="n">
-        <v>-3004978140</v>
+        <v>-935408160</v>
       </c>
       <c r="U5" t="n">
-        <v>12021315830</v>
+        <v>13850784000</v>
       </c>
       <c r="V5" t="n">
-        <v>-5318553080630</v>
+        <v>-8674222881110</v>
       </c>
       <c r="W5" t="n">
-        <v>9097286360650</v>
+        <v>28732441328210</v>
       </c>
       <c r="X5" t="n">
-        <v>-14415839441280</v>
+        <v>-37406664209320</v>
       </c>
       <c r="Y5" t="n">
-        <v>24587523880</v>
+        <v>34543505400</v>
       </c>
       <c r="Z5" t="n">
-        <v>113230681480</v>
+        <v>581909436060</v>
       </c>
       <c r="AA5" t="n">
-        <v>-88643157600</v>
+        <v>-547365930660</v>
       </c>
       <c r="AB5" t="n">
-        <v>-57437774070</v>
+        <v>-176443041530</v>
       </c>
       <c r="AC5" t="n">
-        <v>178716952300</v>
+        <v>133802054360</v>
       </c>
       <c r="AD5" t="n">
-        <v>-236154726370</v>
+        <v>-310245095890</v>
       </c>
       <c r="AE5" t="n">
-        <v>-88983728780</v>
+        <v>-83376181800</v>
       </c>
       <c r="AF5" t="n">
-        <v>19982911790</v>
+        <v>24465587490</v>
       </c>
       <c r="AG5" t="n">
-        <v>-108966640570</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+        <v>-107841769290</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-185719031830</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>19854226800</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>-205573258630</v>
+      </c>
       <c r="AK5" t="n">
-        <v>5560985603760</v>
+        <v>5428575304210</v>
       </c>
       <c r="AL5" t="n">
-        <v>-33285370920</v>
+        <v>-233142680</v>
       </c>
       <c r="AM5" t="n">
-        <v>2908259177730</v>
+        <v>3160306835520</v>
       </c>
       <c r="AN5" t="n">
-        <v>-59169145480</v>
+        <v>-500756954410</v>
       </c>
       <c r="AO5" t="n">
-        <v>614704984410</v>
+        <v>1047380007100</v>
       </c>
       <c r="AP5" t="n">
-        <v>-643084722140</v>
+        <v>1882951736260</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5758000000</v>
+        <v>-481175000000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-611345722000</v>
+        <v>668442736000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-3284042555000</v>
+        <v>-589014160000</v>
       </c>
       <c r="AT5" t="n">
-        <v>7628000000</v>
+        <v>15569000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>4408755000000</v>
+        <v>226589000000</v>
       </c>
       <c r="AV5" t="n">
-        <v>275814000000</v>
+        <v>195800000000</v>
       </c>
       <c r="AW5" t="n">
-        <v>102760000000</v>
+        <v>83507000000</v>
       </c>
       <c r="AX5" t="n">
-        <v>173054000000</v>
+        <v>112293000000</v>
       </c>
       <c r="AY5" t="n">
-        <v>43707000000</v>
+        <v>39142000000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1658687000000</v>
+        <v>1281559000000</v>
       </c>
       <c r="BA5" t="n">
-        <v>-1503165000000</v>
+        <v>-2119335000000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-41945000000</v>
+        <v>-8074000000</v>
       </c>
       <c r="BC5" t="n">
-        <v>1249160234930</v>
+        <v>866000982110</v>
       </c>
     </row>
   </sheetData>
@@ -3125,7 +3125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EU2"/>
+  <dimension ref="A1:EV2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3621,265 +3621,270 @@
       </c>
       <c r="CU1" t="inlineStr">
         <is>
+          <t>earningsGrowth</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3977,7 +3982,7 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="V2" t="n">
         <v>1735603200</v>
@@ -3994,28 +3999,28 @@
         <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>4785</v>
+        <v>5000</v>
       </c>
       <c r="AA2" t="n">
-        <v>4800</v>
+        <v>4955</v>
       </c>
       <c r="AB2" t="n">
-        <v>4700</v>
+        <v>4910</v>
       </c>
       <c r="AC2" t="n">
-        <v>4950</v>
+        <v>5160</v>
       </c>
       <c r="AD2" t="n">
-        <v>4785</v>
+        <v>5000</v>
       </c>
       <c r="AE2" t="n">
-        <v>4800</v>
+        <v>4955</v>
       </c>
       <c r="AF2" t="n">
-        <v>4700</v>
+        <v>4910</v>
       </c>
       <c r="AG2" t="n">
-        <v>4950</v>
+        <v>5160</v>
       </c>
       <c r="AH2" t="n">
         <v>1711584000</v>
@@ -4027,28 +4032,28 @@
         <v>1.93</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.617</v>
+        <v>0.574</v>
       </c>
       <c r="AL2" t="n">
-        <v>6811976</v>
+        <v>1300268</v>
       </c>
       <c r="AM2" t="n">
-        <v>6811976</v>
+        <v>1300268</v>
       </c>
       <c r="AN2" t="n">
-        <v>8799517</v>
+        <v>7698711</v>
       </c>
       <c r="AO2" t="n">
-        <v>10107473</v>
+        <v>8456794</v>
       </c>
       <c r="AP2" t="n">
-        <v>10107473</v>
+        <v>8456794</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4855</v>
+        <v>5000</v>
       </c>
       <c r="AR2" t="n">
-        <v>4860</v>
+        <v>5010</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -4057,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>3647999836160</v>
+        <v>3771979268096</v>
       </c>
       <c r="AV2" t="n">
-        <v>3595402346250</v>
+        <v>3922257105000</v>
       </c>
       <c r="AW2" t="n">
         <v>2930</v>
@@ -4075,13 +4080,13 @@
         <v>881</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.13828872</v>
+        <v>0.13086767</v>
       </c>
       <c r="BB2" t="n">
-        <v>4941</v>
+        <v>5028.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>3851.375</v>
+        <v>3977.9</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -4092,13 +4097,13 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-93539119661056</v>
+        <v>-91209779380224</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.1626186</v>
+        <v>5.3380733</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.026989998</v>
+        <v>0.028110001</v>
       </c>
       <c r="BI2" t="n">
         <v>272491674</v>
@@ -4110,7 +4115,7 @@
         <v>0.55181</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.10672</v>
+        <v>0.10808</v>
       </c>
       <c r="BM2" t="n">
         <v>751390250</v>
@@ -4122,25 +4127,25 @@
         <v>1798675200</v>
       </c>
       <c r="BP2" t="n">
-        <v>1767139200</v>
+        <v>1774915200</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.74</v>
+        <v>0.435</v>
       </c>
       <c r="BR2" t="n">
-        <v>597425979392</v>
+        <v>695759994880</v>
       </c>
       <c r="BS2" t="n">
-        <v>-3.546</v>
+        <v>-3.164</v>
       </c>
       <c r="BT2" t="n">
-        <v>-26.046</v>
+        <v>-25.198</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.55357146</v>
+        <v>0.6036867</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
         <v>150</v>
@@ -4154,7 +4159,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>4855</v>
+        <v>5020</v>
       </c>
       <c r="CA2" t="n">
         <v>7000</v>
@@ -4177,242 +4182,245 @@
         <v>13</v>
       </c>
       <c r="CG2" t="n">
-        <v>121318666141696</v>
+        <v>118892663930880</v>
       </c>
       <c r="CH2" t="n">
-        <v>161458.92</v>
+        <v>158230.25</v>
       </c>
       <c r="CI2" t="n">
-        <v>3591239892992</v>
+        <v>3619697983488</v>
       </c>
       <c r="CJ2" t="n">
-        <v>21383390167040</v>
+        <v>21111335026688</v>
       </c>
       <c r="CK2" t="n">
-        <v>12.884</v>
+        <v>10.438</v>
       </c>
       <c r="CL2" t="n">
-        <v>13.733</v>
+        <v>11.054</v>
       </c>
       <c r="CM2" t="n">
-        <v>26379590565888</v>
+        <v>28822850240512</v>
       </c>
       <c r="CN2" t="n">
-        <v>128.634</v>
+        <v>118.429</v>
       </c>
       <c r="CO2" t="n">
-        <v>34697.145</v>
+        <v>37840.35</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.0124</v>
+        <v>0.01232</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.05865</v>
+        <v>0.0624</v>
       </c>
       <c r="CR2" t="n">
-        <v>10633773842432</v>
+        <v>12921774014464</v>
       </c>
       <c r="CS2" t="n">
-        <v>-2681403867136</v>
+        <v>9109824864256</v>
       </c>
       <c r="CT2" t="n">
-        <v>4377244073984</v>
+        <v>4480563150848</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.298</v>
+        <v>0.425</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.40311</v>
+        <v>0.41</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.13614</v>
+        <v>0.44832</v>
       </c>
       <c r="CX2" t="n">
-        <v>0.07496</v>
-      </c>
-      <c r="CY2" t="inlineStr">
+        <v>0.12558</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>0.09653</v>
+      </c>
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>KRW</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DA2" t="inlineStr">
         <is>
           <t>088350.KS</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DB2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DC2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DD2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DE2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DE2" t="b">
+      <c r="DF2" t="b">
         <v>0</v>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="DG2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>HANWHA LIFE</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>5020</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>KSC</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>finmb_5464612</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>Asia/Seoul</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>KST</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>32400000</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>kr_market</t>
+        </is>
+      </c>
+      <c r="DQ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>1782175235</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-8.299804999999999</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.0016506185</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1042.1001</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.26197243</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>20</v>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1268784000000</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>20</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>4910.0 - 5160.0</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>KSE</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>7698711</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>2090</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>0.7133106</v>
+      </c>
+      <c r="EI2" t="inlineStr">
+        <is>
+          <t>2930.0 - 7560.0</t>
+        </is>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-2540</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.33597884</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>60.368668</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>1786600800</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>1786600800</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>1771826400</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>1771826400</v>
+      </c>
+      <c r="EQ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>760.2118</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>6.603423</v>
+      </c>
+      <c r="ET2" t="inlineStr">
         <is>
           <t>Hanwha Life Insurance Co., Ltd.</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>1780381802</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>KSC</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>finmb_5464612</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Asia/Seoul</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>KST</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>32400000</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>kr_market</t>
-        </is>
-      </c>
-      <c r="DP2" t="b">
+      <c r="EU2" t="b">
         <v>0</v>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>70</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>4700.0 - 4950.0</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>KSE</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>8799517</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1925</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.6569966</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>2930.0 - 7560.0</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>-2705</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.35780424</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>55.357147</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1786600800</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1786600800</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1771826400</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1771826400</v>
-      </c>
-      <c r="EF2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>760.2118</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>6.3863783</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>-86</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-0.017405383</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>1003.625</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.26058877</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>HANWHA LIFE</t>
-        </is>
-      </c>
-      <c r="EP2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>1.4629049</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>4855</v>
-      </c>
-      <c r="ES2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>1268784000000</v>
-      </c>
-      <c r="EU2" t="inlineStr"/>
+      <c r="EV2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
